--- a/public/templates/material_import_template.xlsx
+++ b/public/templates/material_import_template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\PHPEducation_Backend-main\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E95F8F6D-7844-451F-9394-4F122D8D499E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAC8B57A-CFA3-48B2-8815-9F9327F94B41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,38 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
-  <si>
-    <r>
-      <t>ex</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">PHP </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>基礎</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <r>
       <rPr>
@@ -283,32 +252,6 @@
   </si>
   <si>
     <r>
-      <t>topics (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>主題</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
       <t>chapters (</t>
     </r>
     <r>
@@ -397,7 +340,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -448,12 +391,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="細明體"/>
-      <family val="3"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -468,13 +405,6 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Microsoft JhengHei"/>
       <family val="2"/>
     </font>
     <font>
@@ -555,10 +485,10 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -872,16 +802,16 @@
   <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="26.125" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="81.125" customWidth="1"/>
+    <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.75" customWidth="1"/>
+    <col min="3" max="3" width="78" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36" customWidth="1"/>
     <col min="5" max="5" width="25.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="45" customHeight="1">
       <c r="A1" s="7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -890,19 +820,16 @@
     </row>
     <row r="2" spans="1:5" ht="22.05" customHeight="1">
       <c r="A2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="C2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="D2" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="60" customHeight="1">
@@ -913,35 +840,29 @@
         <v>1</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="60" customHeight="1">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="4"/>
+      <c r="D4" s="4"/>
     </row>
     <row r="5" spans="1:5" ht="60" customHeight="1">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="4"/>
+      <c r="D5" s="4"/>
     </row>
     <row r="6" spans="1:5" ht="60" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="4"/>
+      <c r="D6" s="4"/>
     </row>
     <row r="7" spans="1:5" ht="19.95" customHeight="1">
       <c r="A7" s="2"/>
